--- a/output/愛知岐阜三重_赤十字病院_随意契約_X線関連_サマリー.xlsx
+++ b/output/愛知岐阜三重_赤十字病院_随意契約_X線関連_サマリー.xlsx
@@ -620,7 +620,7 @@
         <v>121</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" s="3" t="inlineStr"/>
       <c r="F8" s="3" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>237</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -653,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -785,7 +785,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>外科用イメージ（可搬型Cアーム透視装置）</t>
+          <t>透視撮影台（X線テレビ）</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -817,30 +817,30 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>ＦＰＤシステム保守契約</t>
+          <t>内視鏡用デジタルX線透視撮影装置 １式</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>令和6年3月29日</t>
+          <t>令和5年10月10日</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>8360000</v>
+        <v>31526000</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>透視撮影台（X線テレビ）</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>保守</t>
+          <t>製品</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>㈱エヌケーティー三重県伊勢市御薗町長屋2062-2</t>
+          <t>㈱八神製作所 伊勢営業所伊勢市神久二丁目１番２８号</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -852,30 +852,30 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>三重県</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>日本赤十字社愛知医療センター名古屋第二病院</t>
+          <t>伊勢赤十字病院</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Cアームイメージングシステム保守</t>
+          <t>ＦＰＤシステム保守契約</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>令和7年3月31日</t>
+          <t>令和6年3月29日</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>3120000</v>
+        <v>8360000</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>外科用イメージ（可搬型Cアーム透視装置）</t>
+          <t>一般撮影（レントゲン）</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -885,12 +885,12 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>（株）八神製作所名古屋市中区千代田2-16-30</t>
+          <t>㈱エヌケーティー三重県伊勢市御薗町長屋2062-2</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://www.nagoya2.jrc.or.jp/content/uploads/2025/04/d76b6080924b3169fda065dbe1d20e72.pdf</t>
+          <t>https://www.ise.jrc.or.jp/file/attachment/3638.pdf</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>血管造影X線診断装置（AlluraXper FD20）始め4品目保守</t>
+          <t>Cアームイメージングシステム保守</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -916,11 +916,11 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>48348960</v>
+        <v>3120000</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>血管撮影（CVS、アンギオ）</t>
+          <t>外科用イメージ（可搬型Cアーム透視装置）</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>富士フィルムメディカル（株）名古屋市中区栄1-12-17</t>
+          <t>（株）八神製作所名古屋市中区千代田2-16-30</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -952,33 +952,78 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
+          <t>血管造影X線診断装置（AlluraXper FD20）始め4品目保守</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>令和7年3月31日</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>48348960</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>血管撮影（CVS、アンギオ）</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>保守</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>富士フィルムメディカル（株）名古屋市中区栄1-12-17</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nagoya2.jrc.or.jp/content/uploads/2025/04/d76b6080924b3169fda065dbe1d20e72.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>日本赤十字社愛知医療センター名古屋第二病院</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
           <t>循環器X線診断装置（AlluraClarity）保守</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>令和7年3月31日</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E8" s="5" t="n">
         <v>17226000</v>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>血管撮影（CVS、アンギオ）</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>保守</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>（株）APEX名古屋市西区康生通2-26</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>https://www.nagoya2.jrc.or.jp/content/uploads/2025/04/d76b6080924b3169fda065dbe1d20e72.pdf</t>
         </is>
